--- a/tiflow-diga/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-LOG-MedicationDispense-DiGA.xlsx
+++ b/tiflow-diga/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-LOG-MedicationDispense-DiGA.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -329,6 +329,9 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>GEM-ERP-LOG-MedicationDispense-DiGA.prescriptionId</t>
   </si>
   <si>
@@ -434,9 +437,6 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>GEM-ERP-LOG-MedicationDispense-DiGA.angabenZurDiGA.name</t>
@@ -1270,7 +1270,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>101</v>
@@ -1279,15 +1279,15 @@
         <v>76</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>84</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1313,10 +1313,10 @@
         <v>87</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1367,7 +1367,7 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>86</v>
@@ -1382,7 +1382,7 @@
         <v>76</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>76</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1416,13 +1416,13 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1473,7 +1473,7 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>86</v>
@@ -1488,7 +1488,7 @@
         <v>76</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>76</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1525,10 +1525,10 @@
         <v>87</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1579,7 +1579,7 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>86</v>
@@ -1594,7 +1594,7 @@
         <v>76</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>76</v>
@@ -1602,10 +1602,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1628,13 +1628,13 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1685,7 +1685,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>86</v>
@@ -1700,7 +1700,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>76</v>
@@ -1708,10 +1708,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1737,10 +1737,10 @@
         <v>87</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1791,7 +1791,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -1806,7 +1806,7 @@
         <v>76</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>76</v>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1843,10 +1843,10 @@
         <v>87</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1897,7 +1897,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -1912,7 +1912,7 @@
         <v>76</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>76</v>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1946,13 +1946,13 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2003,7 +2003,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2018,7 +2018,7 @@
         <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>76</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2132,10 +2132,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2240,14 +2240,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2260,25 +2260,25 @@
         <v>76</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>96</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>76</v>
@@ -2327,7 +2327,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2336,7 +2336,7 @@
         <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>101</v>
@@ -2345,7 +2345,7 @@
         <v>76</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>136</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -2588,7 +2588,7 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s" s="2">
         <v>144</v>
@@ -2906,7 +2906,7 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>155</v>
